--- a/data/Table-Data-Base.xlsx
+++ b/data/Table-Data-Base.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\Pleistocene_Human_Use_Of_Caves-master\Pleistocene_Human_Use_Of_Caves-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830417B0-920B-4DEF-9C99-1A7713D91E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB23C55-32A2-4ACA-9E44-D77E8F2FE018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
   </bookViews>
@@ -10951,9 +10951,6 @@
     <t>1.67665223850152922</t>
   </si>
   <si>
-    <t>44.06316397904677729)</t>
-  </si>
-  <si>
     <t>0.38078583229196156</t>
   </si>
   <si>
@@ -11101,6 +11098,9 @@
   </si>
   <si>
     <t>Garate &amp; Rivero, 2026</t>
+  </si>
+  <si>
+    <t>44.06316397904677729</t>
   </si>
 </sst>
 </file>
@@ -12484,7 +12484,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>173</v>
@@ -13050,10 +13050,10 @@
         <v>1367</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>3275</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>3276</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>3277</v>
       </c>
       <c r="E21" s="8">
         <v>25</v>
@@ -15167,7 +15167,7 @@
         <v>3272</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>3273</v>
+        <v>3292</v>
       </c>
       <c r="E55" s="3">
         <v>150</v>
@@ -23090,10 +23090,10 @@
         <v>1361</v>
       </c>
       <c r="C181" s="11" t="s">
+        <v>3277</v>
+      </c>
+      <c r="D181" s="11" t="s">
         <v>3278</v>
-      </c>
-      <c r="D181" s="11" t="s">
-        <v>3279</v>
       </c>
       <c r="E181" s="8">
         <v>448</v>
@@ -24303,10 +24303,10 @@
         <v>1361</v>
       </c>
       <c r="C200" s="8" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D200" s="8" t="s">
         <v>3274</v>
-      </c>
-      <c r="D200" s="8" t="s">
-        <v>3275</v>
       </c>
       <c r="E200" s="8">
         <v>86</v>
@@ -32175,10 +32175,10 @@
         <v>1361</v>
       </c>
       <c r="C324" s="13" t="s">
+        <v>3279</v>
+      </c>
+      <c r="D324" s="13" t="s">
         <v>3280</v>
-      </c>
-      <c r="D324" s="13" t="s">
-        <v>3281</v>
       </c>
       <c r="E324" s="12">
         <v>220</v>
@@ -38184,7 +38184,7 @@
     </row>
     <row r="421" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="12" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B421" s="12" t="s">
         <v>1550</v>
@@ -38247,7 +38247,7 @@
     </row>
     <row r="422" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="12" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B422" s="12" t="s">
         <v>1351</v>
@@ -38310,7 +38310,7 @@
     </row>
     <row r="423" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="12" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B423" s="12" t="s">
         <v>1351</v>
@@ -38379,7 +38379,7 @@
     </row>
     <row r="424" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="12" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B424" s="12" t="s">
         <v>1351</v>
@@ -38450,7 +38450,7 @@
     </row>
     <row r="425" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="12" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B425" s="12" t="s">
         <v>1551</v>
@@ -40500,7 +40500,7 @@
         <v>270</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>1232</v>
@@ -40535,7 +40535,7 @@
         <v>60</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="K23" s="33" t="s">
         <v>1317</v>
@@ -58589,7 +58589,7 @@
         <v>2597</v>
       </c>
       <c r="C535" s="33" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="D535" s="33" t="s">
         <v>805</v>
@@ -58624,7 +58624,7 @@
         <v>2597</v>
       </c>
       <c r="C536" s="33" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="D536" s="33" t="s">
         <v>805</v>
@@ -58659,7 +58659,7 @@
         <v>2597</v>
       </c>
       <c r="C537" s="33" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="D537" s="33" t="s">
         <v>805</v>
@@ -58729,7 +58729,7 @@
         <v>2597</v>
       </c>
       <c r="C539" s="33" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="D539" s="33" t="s">
         <v>805</v>
@@ -58834,7 +58834,7 @@
         <v>2597</v>
       </c>
       <c r="C542" s="33" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="D542" s="33" t="s">
         <v>805</v>
@@ -58846,7 +58846,7 @@
         <v>676</v>
       </c>
       <c r="G542" s="33" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="H542" s="33">
         <v>14815</v>
@@ -58855,7 +58855,7 @@
         <v>70</v>
       </c>
       <c r="J542" s="33" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="K542" s="33" t="s">
         <v>1317</v>
@@ -58881,7 +58881,7 @@
         <v>676</v>
       </c>
       <c r="G543" s="33" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="H543" s="33">
         <v>13840</v>
@@ -58890,7 +58890,7 @@
         <v>65</v>
       </c>
       <c r="J543" s="33" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="K543" s="33" t="s">
         <v>1317</v>
@@ -60077,7 +60077,7 @@
         <v>2707</v>
       </c>
       <c r="K577" s="33" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.3">
@@ -67075,7 +67075,7 @@
     </row>
     <row r="771" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A771" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B771" s="7" t="s">
         <v>3203</v>
@@ -67110,7 +67110,7 @@
     </row>
     <row r="772" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A772" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3206</v>
@@ -67145,7 +67145,7 @@
     </row>
     <row r="773" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A773" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B773" s="7" t="s">
         <v>3206</v>
@@ -67180,7 +67180,7 @@
     </row>
     <row r="774" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A774" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B774" s="7" t="s">
         <v>3206</v>
@@ -67215,7 +67215,7 @@
     </row>
     <row r="775" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A775" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B775" s="7" t="s">
         <v>3206</v>
@@ -67250,7 +67250,7 @@
     </row>
     <row r="776" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A776" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B776" s="7" t="s">
         <v>3180</v>
@@ -67285,7 +67285,7 @@
     </row>
     <row r="777" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A777" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B777" s="7" t="s">
         <v>3183</v>
@@ -67320,7 +67320,7 @@
     </row>
     <row r="778" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A778" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B778" s="7" t="s">
         <v>3178</v>
@@ -67355,7 +67355,7 @@
     </row>
     <row r="779" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A779" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B779" s="7" t="s">
         <v>3185</v>
@@ -67390,7 +67390,7 @@
     </row>
     <row r="780" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A780" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B780" s="7" t="s">
         <v>3201</v>
@@ -67425,7 +67425,7 @@
     </row>
     <row r="781" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A781" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B781" s="7" t="s">
         <v>3198</v>
@@ -67460,7 +67460,7 @@
     </row>
     <row r="782" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A782" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B782" s="7" t="s">
         <v>3190</v>
@@ -67495,7 +67495,7 @@
     </row>
     <row r="783" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A783" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3188</v>
@@ -67530,7 +67530,7 @@
     </row>
     <row r="784" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A784" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B784" s="7" t="s">
         <v>3196</v>
@@ -67565,7 +67565,7 @@
     </row>
     <row r="785" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A785" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B785" s="7" t="s">
         <v>3194</v>
@@ -67600,7 +67600,7 @@
     </row>
     <row r="786" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A786" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B786" s="7" t="s">
         <v>3192</v>
@@ -67635,7 +67635,7 @@
     </row>
     <row r="787" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A787" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B787" s="7" t="s">
         <v>3173</v>
@@ -67670,7 +67670,7 @@
     </row>
     <row r="788" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A788" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B788" s="7" t="s">
         <v>3176</v>
